--- a/word/Kiểm thử chức năng..xlsx
+++ b/word/Kiểm thử chức năng..xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Doan4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Doan4\word\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900957E1-F990-463D-9934-5342CA542577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1289F8-126E-41C5-BAD6-963CFA4570A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Đăng Ký" sheetId="1" r:id="rId1"/>
     <sheet name="Đăng nhập" sheetId="4" r:id="rId2"/>
     <sheet name="Tìm kiếm " sheetId="2" r:id="rId3"/>
     <sheet name="Thông tin tài khoản" sheetId="9" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId5"/>
+    <sheet name="Đặt hàng" sheetId="12" r:id="rId5"/>
     <sheet name="Báo cáo tổng kết " sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="405">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -1346,110 +1346,13 @@
 “Mật khâu mới không chính xác.”</t>
   </si>
   <si>
-    <t>tukhoa</t>
-  </si>
-  <si>
-    <t>tensp</t>
-  </si>
-  <si>
-    <t>ten</t>
-  </si>
-  <si>
-    <t>diachi</t>
-  </si>
-  <si>
-    <t>thanhpho</t>
-  </si>
-  <si>
-    <t>sdt</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>ghichu</t>
-  </si>
-  <si>
-    <t>ketquamongdoi</t>
-  </si>
-  <si>
-    <t>trơn nâu</t>
-  </si>
-  <si>
-    <t>Ly Giấy Nâu Trơn 16oz</t>
-  </si>
-  <si>
-    <t>nam</t>
-  </si>
-  <si>
-    <t>Hà Nội</t>
-  </si>
-  <si>
-    <t>0122336523</t>
-  </si>
-  <si>
-    <t>nguyennam@gmail.com</t>
-  </si>
-  <si>
-    <t>không</t>
-  </si>
-  <si>
     <t>Mục Địa chỉ là mục bắt buộc.</t>
   </si>
   <si>
     <t>Mục Tên là mục bắt buộc.</t>
   </si>
   <si>
-    <t>vĩnh tuy</t>
-  </si>
-  <si>
-    <t>0122336524</t>
-  </si>
-  <si>
-    <t>0122336525</t>
-  </si>
-  <si>
-    <t>0122336527</t>
-  </si>
-  <si>
-    <t>0122336528</t>
-  </si>
-  <si>
-    <t>0122336529</t>
-  </si>
-  <si>
-    <t>Mục Thị trấn / Thành phố là mục bắt buộc.</t>
-  </si>
-  <si>
-    <t>Mục Số điện thoại là mục bắt buộc.</t>
-  </si>
-  <si>
-    <t>Mục Địa chỉ email là mục bắt buộc.</t>
-  </si>
-  <si>
     <t>Cảm ơn bạn. Đơn hàng của bạn đã được nhận.</t>
-  </si>
-  <si>
-    <t>Mục Tên là mục bắt buộc.
-Mục Địa chỉ là mục bắt buộc.</t>
-  </si>
-  <si>
-    <t>nguyennam</t>
-  </si>
-  <si>
-    <t>Mục Địa chỉ email không phải là địa chỉ email hợp lệ.</t>
-  </si>
-  <si>
-    <t>0122336530</t>
-  </si>
-  <si>
-    <t>nguyennam@@gmail.com</t>
-  </si>
-  <si>
-    <t>lieuly@gmail.com2</t>
-  </si>
-  <si>
-    <t>lieuly@gmail.com3</t>
   </si>
   <si>
     <t>Emai sai</t>
@@ -1468,13 +1371,309 @@
   </si>
   <si>
     <t>TC-DK15</t>
+  </si>
+  <si>
+    <t>TC01</t>
+  </si>
+  <si>
+    <t>Kiểm tra thông báo khi không nhập Tên</t>
+  </si>
+  <si>
+    <t>TC02</t>
+  </si>
+  <si>
+    <t>Bỏ trống Địa chỉ</t>
+  </si>
+  <si>
+    <t>Kiểm tra thông báo khi không nhập Địa chỉ</t>
+  </si>
+  <si>
+    <t>TC03</t>
+  </si>
+  <si>
+    <t>Bỏ trống Thành phố</t>
+  </si>
+  <si>
+    <t>Kiểm tra thông báo khi không chọn Thành phố</t>
+  </si>
+  <si>
+    <t>TC04</t>
+  </si>
+  <si>
+    <t>Bỏ trống SĐT</t>
+  </si>
+  <si>
+    <t>Kiểm tra thông báo khi không nhập SĐT</t>
+  </si>
+  <si>
+    <t>TC05</t>
+  </si>
+  <si>
+    <t>Kiểm tra thông báo khi không nhập Email</t>
+  </si>
+  <si>
+    <t>TC06</t>
+  </si>
+  <si>
+    <t>Nhập dữ liệu hợp lệ</t>
+  </si>
+  <si>
+    <t>Đặt hàng thành công với dữ liệu đúng</t>
+  </si>
+  <si>
+    <t>TC07</t>
+  </si>
+  <si>
+    <t>Bỏ trống Tên và Địa chỉ</t>
+  </si>
+  <si>
+    <t>Kiểm tra validate nhiều trường bắt buộc</t>
+  </si>
+  <si>
+    <t>Mục Tên là mục bắt buộc.Mục Địa chỉ là mục bắt buộc.</t>
+  </si>
+  <si>
+    <t>TC08</t>
+  </si>
+  <si>
+    <t>Email sai định dạng</t>
+  </si>
+  <si>
+    <t>Kiểm tra Email không hợp lệ</t>
+  </si>
+  <si>
+    <t>Mục Địa chỉ email không phải là địa chỉ email hợp lệ</t>
+  </si>
+  <si>
+    <t>TC09</t>
+  </si>
+  <si>
+    <t>Email có 2 dấu @</t>
+  </si>
+  <si>
+    <t>Kiểm tra Email chứa 2 dấu @</t>
+  </si>
+  <si>
+    <t>TC10</t>
+  </si>
+  <si>
+    <t>Email có số cuối</t>
+  </si>
+  <si>
+    <t>Đặt hàng thành công với Email có số</t>
+  </si>
+  <si>
+    <t>TC11</t>
+  </si>
+  <si>
+    <t>SĐT ngắn</t>
+  </si>
+  <si>
+    <t>Đặt hàng thành công với SĐT ngắn</t>
+  </si>
+  <si>
+    <t>1. Truy cập website
+2. Nhập từ khóa trơn nâu
+3. Nhấn tìm kiếm
+4. Chọn SP Ly Giấy Nâu Trơn 16oz
+5. Không nhập Tên
+6. Nhập Địa chỉ: vĩnh tuy
+7. Chọn Thành phố: Hà Nội
+8. Nhập SĐT: 0122336523
+9. Nhập Email: nguyennam@gmail.com
+10. Nhập Ghi chú: không
+11. Nhấn Đặt hàng</t>
+  </si>
+  <si>
+    <t>1. Truy cập website
+2. Tìm kiếm trơn nâu
+3. Chọn Ly Giấy Nâu Trơn 16oz
+4. Nhập Tên: nam
+5. Không nhập Địa chỉ
+6. Chọn Thành phố: Hà Nội
+7. Nhập SĐT: 01223365248. Nhập Email: nguyennam@gmail.com
+9. Nhập Ghi chú: không
+10. Nhấn Đặt hàng</t>
+  </si>
+  <si>
+    <t>1. Truy cập website
+2. Tìm kiếm trơn nâu
+3. Chọn sản phẩm
+4. Nhập Tên: nam
+5. Nhập Địa chỉ: vĩnh tuy
+6. Không chọn Thành phố
+7. Nhập SĐT: 0122336525
+8. Nhập Email: nguyennam@gmail.com
+9. Nhập Ghi chú: không
+10. Nhấn Đặt hàng</t>
+  </si>
+  <si>
+    <t>1. Truy cập website
+2. Tìm kiếm trơn nâu
+3. Chọn sản phẩm
+4. Nhập Tên: nam
+5. Nhập Địa chỉ: vĩnh tuy
+6. Chọn Thành phố: Hà Nội
+7. Không nhập SĐT
+8. Nhập Email: nguyennam@gmail.com
+9. Nhập Ghi chú: không
+10. Nhấn Đặt hàng</t>
+  </si>
+  <si>
+    <t>1. Truy cập website
+2. Tìm kiếm trơn nâu
+3. Chọn sản phẩm
+4. Nhập Tên: nam
+5. Nhập Địa chỉ: vĩnh tuy
+6. Chọn Thành phố: Hà Nội
+7. Nhập SĐT: 0122336528
+8. Nhập Email: nguyennam@gmail.com
+9. Không nhập Ghi chú
+10. Nhấn Đặt hàng</t>
+  </si>
+  <si>
+    <t>Mục Thị trấn / Thành phố là mục bắt buộc.</t>
+  </si>
+  <si>
+    <t>Mục Số điện thoại là mục bắt buộc.</t>
+  </si>
+  <si>
+    <t>Mục Địa chỉ email là mục bắt buộc.</t>
+  </si>
+  <si>
+    <t>1. Truy cập website
+2. Tìm kiếm trơn nâu
+3. Chọn sản phẩm
+4. Không nhập Tên
+5. Không nhập Địa chỉ
+6. Chọn Thành phố: Hà Nội
+7. Nhập SĐT: 0122336529
+8. Nhập Email: nguyennam@gmail.com
+9. Nhập Ghi chú: không
+10. Nhấn Đặt hàng</t>
+  </si>
+  <si>
+    <t>Mục Địa chỉ email không phải là địa chỉ email hợp lệ.</t>
+  </si>
+  <si>
+    <t>1. Truy cập website
+2. Tìm kiếm trơn nâu
+3. Chọn sản phẩm
+4. Nhập Tên: nam
+5. Nhập Địa chỉ: vĩnh tu
+y6. Chọn Thành phố: Hà Nội
+7. Nhập SĐT: 0122336529
+8. Nhập Email: nguyennam
+9. Nhấn Đặt hàng</t>
+  </si>
+  <si>
+    <t>1. Truy cập website
+2. Tìm kiếm trơn nâu
+3. Chọn sản phẩm
+4. Nhập Tên: nam
+5. Nhập Địa chỉ: vĩnh tuy
+6. Chọn Thành phố: Hà Nội
+7. Nhập SĐT: 0122336530
+8. Nhập Email: nguyennam@@gmail.com
+9. Nhấn Đặt hàng</t>
+  </si>
+  <si>
+    <t>1. Truy cập website
+2. Tìm kiếm trơn nâu
+3. Chọn sản phẩm
+4. Nhập Tên: nam
+5. Nhập Địa chỉ: vĩnh tuy
+6. Chọn Thành phố: Hà Nội
+7. Nhập SĐT: 0122336530
+8. Nhập Email: lieuly@gmail.com2
+9. Nhấn Đặt hàng</t>
+  </si>
+  <si>
+    <t>1. Truy cập website
+2. Tìm kiếm trơn nâu
+3. Chọn sản phẩm
+4. Nhập Tên: nam
+5. Nhập Địa chỉ: vĩnh tuy
+6. Chọn Thành phố: Hà Nội
+7. Nhập SĐT: 2122
+8. Nhập Email: lieuly@gmail.com3
+9. Nhấn Đặt hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đặt hàng </t>
+  </si>
+  <si>
+    <r>
+      <t>1. Truy cập website
+2. Tìm kiếm trơn nâu</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>3. Chọn sản phẩm
+4. Nhập Tên: nam
+5. Nhập Địa chỉ: vĩnh tuy
+6. Chọn Thành phố: Hà Nội
+7. Nhập SĐT: 0122336527
+8. Không nhập Email</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>9. Nhập Ghi chú: không
+10. Nhấn Đặt hàng</t>
+    </r>
+  </si>
+  <si>
+    <t>Đang ở Trang chủ</t>
+  </si>
+  <si>
+    <t>1. Truy cập website
+2. Tìm kiếm trơn nâu
+3. Chọn sản phẩm
+4. Nhập Tên: nam
+5. Nhập Địa chỉ: vĩnh tu
+y6. Chọn Thành phố: Hà Nội
+7. Nhập SĐT: 0122336529
+8. Nhập Email: G19
+9. Nhấn Đặt hàng</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1493,13 +1692,6 @@
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="9"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1532,13 +1724,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="9"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -1548,32 +1733,6 @@
       <sz val="8"/>
       <color theme="0"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -1596,18 +1755,45 @@
       <family val="1"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="13"/>
+      <color indexed="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1666,7 +1852,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1962,41 +2148,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -2008,179 +2165,214 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2189,18 +2381,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Sheet1" xfId="1" xr:uid="{6EF5C705-D68B-4323-9104-7B3EB48FFC04}"/>
   </cellStyles>
@@ -2496,592 +2687,592 @@
     <row r="1" spans="1:14" ht="30">
       <c r="E1" s="5"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="K1"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="E2" s="74"/>
-      <c r="F2" s="75"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="88"/>
       <c r="G2" s="4"/>
       <c r="K2"/>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="72" t="s">
+    <row r="3" spans="1:14" ht="16.8">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="73"/>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="86"/>
+      <c r="G3" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="72" t="s">
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:14" ht="16.8">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="73"/>
-      <c r="G4" s="17" t="s">
+      <c r="F4" s="86"/>
+      <c r="G4" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="72" t="s">
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+    </row>
+    <row r="5" spans="1:14" ht="16.8">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="73"/>
-      <c r="G5" s="18">
+      <c r="F5" s="86"/>
+      <c r="G5" s="60">
         <v>45516</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="72" t="s">
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+    </row>
+    <row r="6" spans="1:14" ht="16.8">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="73"/>
-      <c r="G6" s="18">
+      <c r="F6" s="86"/>
+      <c r="G6" s="60">
         <v>41985</v>
       </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="72" t="s">
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+    </row>
+    <row r="7" spans="1:14" ht="16.8">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="73"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19" t="s">
+      <c r="F7" s="86"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+    </row>
+    <row r="8" spans="1:14" ht="16.8">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="61">
         <v>15</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19" t="s">
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+    </row>
+    <row r="9" spans="1:14" ht="16.8">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="61">
         <v>13</v>
       </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="20" t="s">
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+    </row>
+    <row r="10" spans="1:14" ht="16.8">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="63">
         <v>2</v>
       </c>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-    </row>
-    <row r="11" spans="1:14" s="26" customFormat="1" ht="51" thickBot="1">
-      <c r="A11" s="60" t="s">
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+    </row>
+    <row r="11" spans="1:14" s="17" customFormat="1" ht="51" thickBot="1">
+      <c r="A11" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="60" t="s">
+      <c r="C11" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="60" t="s">
+      <c r="D11" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="61" t="s">
+      <c r="E11" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="61" t="s">
+      <c r="G11" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="60" t="s">
+      <c r="H11" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="I11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="23" t="s">
+      <c r="J11" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
     </row>
     <row r="12" spans="1:14" ht="67.8" thickBot="1">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="35" t="s">
         <v>254</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="D12" s="62" t="s">
+      <c r="D12" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="E12" s="35" t="s">
         <v>256</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F12" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="35" t="s">
         <v>258</v>
       </c>
-      <c r="H12" s="62" t="s">
+      <c r="H12" s="35" t="s">
         <v>21</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" ht="67.8" thickBot="1">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="62" t="s">
+      <c r="B13" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="35" t="s">
         <v>260</v>
       </c>
-      <c r="D13" s="62" t="s">
+      <c r="D13" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="62" t="s">
+      <c r="E13" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="F13" s="62" t="s">
+      <c r="F13" s="35" t="s">
         <v>261</v>
       </c>
-      <c r="G13" s="62" t="s">
+      <c r="G13" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="H13" s="62" t="s">
+      <c r="H13" s="35" t="s">
         <v>21</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" ht="67.8" thickBot="1">
-      <c r="A14" s="62" t="s">
+      <c r="A14" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="62" t="s">
+      <c r="B14" s="35" t="s">
         <v>263</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="35" t="s">
         <v>264</v>
       </c>
-      <c r="D14" s="62" t="s">
+      <c r="D14" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="62" t="s">
+      <c r="E14" s="35" t="s">
         <v>320</v>
       </c>
-      <c r="F14" s="62" t="s">
+      <c r="F14" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="G14" s="62" t="s">
+      <c r="G14" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="H14" s="62" t="s">
+      <c r="H14" s="35" t="s">
         <v>21</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" ht="67.8" thickBot="1">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="62" t="s">
+      <c r="B15" s="35" t="s">
         <v>266</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="35" t="s">
         <v>267</v>
       </c>
-      <c r="D15" s="62" t="s">
+      <c r="D15" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="F15" s="62" t="s">
+      <c r="F15" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="G15" s="62" t="s">
+      <c r="G15" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="H15" s="62" t="s">
+      <c r="H15" s="35" t="s">
         <v>21</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" ht="84.6" thickBot="1">
-      <c r="A16" s="62" t="s">
+      <c r="A16" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="62" t="s">
+      <c r="B16" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="C16" s="62" t="s">
+      <c r="C16" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="D16" s="62" t="s">
+      <c r="D16" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="62" t="s">
+      <c r="E16" s="35" t="s">
         <v>321</v>
       </c>
-      <c r="F16" s="62" t="s">
+      <c r="F16" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="35" t="s">
         <v>21</v>
       </c>
       <c r="K16"/>
     </row>
     <row r="17" spans="1:11" ht="67.8" thickBot="1">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="62" t="s">
+      <c r="B17" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="C17" s="62" t="s">
+      <c r="C17" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="D17" s="62" t="s">
+      <c r="D17" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="62" t="s">
+      <c r="E17" s="35" t="s">
         <v>276</v>
       </c>
-      <c r="F17" s="62" t="s">
+      <c r="F17" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="G17" s="62" t="s">
+      <c r="G17" s="35" t="s">
         <v>278</v>
       </c>
-      <c r="H17" s="62" t="s">
+      <c r="H17" s="35" t="s">
         <v>21</v>
       </c>
       <c r="K17"/>
     </row>
     <row r="18" spans="1:11" ht="126.6" customHeight="1" thickBot="1">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="62" t="s">
+      <c r="B18" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="C18" s="62" t="s">
+      <c r="C18" s="35" t="s">
         <v>343</v>
       </c>
-      <c r="D18" s="62" t="s">
+      <c r="D18" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="62" t="s">
+      <c r="E18" s="35" t="s">
         <v>280</v>
       </c>
-      <c r="F18" s="62" t="s">
+      <c r="F18" s="35" t="s">
         <v>342</v>
       </c>
-      <c r="G18" s="62" t="s">
+      <c r="G18" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="H18" s="62" t="s">
+      <c r="H18" s="35" t="s">
         <v>23</v>
       </c>
       <c r="K18"/>
     </row>
     <row r="19" spans="1:11" ht="133.19999999999999" customHeight="1" thickBot="1">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="35" t="s">
         <v>312</v>
       </c>
-      <c r="B19" s="62" t="s">
+      <c r="B19" s="35" t="s">
         <v>282</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C19" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="D19" s="62" t="s">
+      <c r="D19" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="62" t="s">
+      <c r="E19" s="35" t="s">
         <v>284</v>
       </c>
-      <c r="F19" s="62" t="s">
+      <c r="F19" s="35" t="s">
         <v>285</v>
       </c>
-      <c r="G19" s="62" t="s">
+      <c r="G19" s="35" t="s">
         <v>285</v>
       </c>
-      <c r="H19" s="62" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
+      <c r="H19" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
     </row>
     <row r="20" spans="1:11" ht="67.8" thickBot="1">
-      <c r="A20" s="62" t="s">
+      <c r="A20" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="C20" s="62" t="s">
+      <c r="C20" s="35" t="s">
         <v>287</v>
       </c>
-      <c r="D20" s="62" t="s">
+      <c r="D20" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="62" t="s">
+      <c r="E20" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="F20" s="62" t="s">
+      <c r="F20" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="G20" s="62" t="s">
+      <c r="G20" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="H20" s="62" t="s">
+      <c r="H20" s="35" t="s">
         <v>21</v>
       </c>
       <c r="K20"/>
     </row>
     <row r="21" spans="1:11" ht="67.8" thickBot="1">
-      <c r="A21" s="62" t="s">
+      <c r="A21" s="35" t="s">
         <v>314</v>
       </c>
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="C21" s="62" t="s">
+      <c r="C21" s="35" t="s">
         <v>291</v>
       </c>
-      <c r="D21" s="62" t="s">
+      <c r="D21" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="62" t="s">
+      <c r="E21" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="F21" s="62" t="s">
+      <c r="F21" s="35" t="s">
         <v>281</v>
       </c>
-      <c r="G21" s="62" t="s">
+      <c r="G21" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="H21" s="62" t="s">
+      <c r="H21" s="35" t="s">
         <v>23</v>
       </c>
       <c r="K21"/>
     </row>
     <row r="22" spans="1:11" ht="67.8" thickBot="1">
-      <c r="A22" s="62" t="s">
+      <c r="A22" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="B22" s="62" t="s">
+      <c r="B22" s="35" t="s">
         <v>294</v>
       </c>
-      <c r="C22" s="62" t="s">
+      <c r="C22" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="D22" s="62" t="s">
+      <c r="D22" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="62" t="s">
+      <c r="E22" s="35" t="s">
         <v>296</v>
       </c>
-      <c r="F22" s="62" t="s">
+      <c r="F22" s="35" t="s">
         <v>297</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="H22" s="62" t="s">
+      <c r="H22" s="35" t="s">
         <v>21</v>
       </c>
       <c r="K22"/>
     </row>
     <row r="23" spans="1:11" ht="84.6" thickBot="1">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="B23" s="62" t="s">
+      <c r="B23" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="C23" s="62" t="s">
+      <c r="C23" s="35" t="s">
         <v>300</v>
       </c>
-      <c r="D23" s="62" t="s">
+      <c r="D23" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="62" t="s">
+      <c r="E23" s="35" t="s">
         <v>301</v>
       </c>
-      <c r="F23" s="62" t="s">
+      <c r="F23" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="G23" s="62" t="s">
+      <c r="G23" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="H23" s="62" t="s">
+      <c r="H23" s="35" t="s">
         <v>21</v>
       </c>
       <c r="K23"/>
     </row>
     <row r="24" spans="1:11" ht="67.8" thickBot="1">
-      <c r="A24" s="62" t="s">
+      <c r="A24" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="B24" s="62" t="s">
+      <c r="B24" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="35" t="s">
         <v>193</v>
       </c>
-      <c r="D24" s="62" t="s">
+      <c r="D24" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="62" t="s">
+      <c r="E24" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="F24" s="62" t="s">
+      <c r="F24" s="35" t="s">
         <v>306</v>
       </c>
-      <c r="G24" s="62" t="s">
+      <c r="G24" s="35" t="s">
         <v>307</v>
       </c>
-      <c r="H24" s="62" t="s">
+      <c r="H24" s="35" t="s">
         <v>21</v>
       </c>
       <c r="K24"/>
     </row>
     <row r="25" spans="1:11" ht="67.8" thickBot="1">
-      <c r="A25" s="62" t="s">
+      <c r="A25" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="B25" s="62" t="s">
+      <c r="B25" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="C25" s="62" t="s">
+      <c r="C25" s="35" t="s">
         <v>196</v>
       </c>
-      <c r="D25" s="62" t="s">
+      <c r="D25" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="62" t="s">
+      <c r="E25" s="35" t="s">
         <v>309</v>
       </c>
-      <c r="F25" s="62" t="s">
+      <c r="F25" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="G25" s="62" t="s">
+      <c r="G25" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="H25" s="62" t="s">
+      <c r="H25" s="35" t="s">
         <v>21</v>
       </c>
       <c r="K25"/>
     </row>
     <row r="26" spans="1:11" ht="67.8" thickBot="1">
-      <c r="A26" s="62" t="s">
-        <v>385</v>
-      </c>
-      <c r="B26" s="62" t="s">
-        <v>381</v>
-      </c>
-      <c r="C26" s="62" t="s">
-        <v>382</v>
-      </c>
-      <c r="D26" s="62" t="s">
+      <c r="A26" s="35" t="s">
+        <v>353</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>349</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>350</v>
+      </c>
+      <c r="D26" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E26" s="62" t="s">
-        <v>384</v>
-      </c>
-      <c r="F26" s="62" t="s">
-        <v>383</v>
-      </c>
-      <c r="G26" s="62" t="s">
-        <v>383</v>
-      </c>
-      <c r="H26" s="62" t="s">
+      <c r="E26" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="F26" s="35" t="s">
+        <v>351</v>
+      </c>
+      <c r="G26" s="35" t="s">
+        <v>351</v>
+      </c>
+      <c r="H26" s="35" t="s">
         <v>21</v>
       </c>
       <c r="K26"/>
@@ -3188,9 +3379,9 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H11 H58:H1048576" xr:uid="{889156AC-2F61-4A4A-A2AB-6C02BE03346D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576" xr:uid="{889156AC-2F61-4A4A-A2AB-6C02BE03346D}">
       <formula1>"Pass,Fail"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3204,107 +3395,108 @@
   <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="23.21875" style="10" customWidth="1"/>
-    <col min="3" max="3" width="44.88671875" style="10" customWidth="1"/>
-    <col min="4" max="4" width="34.5546875" style="10" customWidth="1"/>
-    <col min="5" max="5" width="37.109375" style="10" customWidth="1"/>
-    <col min="6" max="6" width="50.77734375" style="10" customWidth="1"/>
-    <col min="7" max="7" width="42.44140625" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="10"/>
+    <col min="1" max="1" width="11.44140625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="57.33203125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="44.88671875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="34.5546875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="37.109375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="50.77734375" style="9" customWidth="1"/>
+    <col min="7" max="7" width="42.44140625" style="9" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="E1" s="76" t="s">
+    <row r="1" spans="1:11" ht="16.8">
+      <c r="E1" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="77"/>
-      <c r="G1" s="29" t="s">
+      <c r="F1" s="90"/>
+      <c r="G1" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="32"/>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="E2" s="76" t="s">
+      <c r="H1" s="19"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="21"/>
+    </row>
+    <row r="2" spans="1:11" ht="16.8">
+      <c r="E2" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="77"/>
-      <c r="G2" s="29" t="s">
+      <c r="F2" s="90"/>
+      <c r="G2" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="34"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="E3" s="76" t="s">
+      <c r="H2" s="19"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="23"/>
+    </row>
+    <row r="3" spans="1:11" ht="16.8">
+      <c r="E3" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="77"/>
-      <c r="G3" s="35">
+      <c r="F3" s="90"/>
+      <c r="G3" s="67">
         <v>45516</v>
       </c>
-      <c r="H3" s="36"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="38"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="E4" s="76" t="s">
+      <c r="H3" s="24"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="26"/>
+    </row>
+    <row r="4" spans="1:11" ht="16.8">
+      <c r="E4" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="77"/>
-      <c r="G4" s="35">
+      <c r="F4" s="90"/>
+      <c r="G4" s="67">
         <v>41985</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="40"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="E5" s="76" t="s">
+      <c r="H4" s="27"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="28"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.8">
+      <c r="E5" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="77"/>
-      <c r="G5" s="29"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="34"/>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="E6" s="41"/>
-      <c r="F6" s="41" t="s">
+      <c r="F5" s="90"/>
+      <c r="G5" s="66"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="23"/>
+    </row>
+    <row r="6" spans="1:11" ht="16.8">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="68">
         <v>11</v>
       </c>
-      <c r="I6" s="32"/>
-      <c r="J6" s="34"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="E7" s="41"/>
-      <c r="F7" s="41" t="s">
+      <c r="I6" s="21"/>
+      <c r="J6" s="23"/>
+    </row>
+    <row r="7" spans="1:11" ht="16.8">
+      <c r="E7" s="68"/>
+      <c r="F7" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="68">
         <v>11</v>
       </c>
-      <c r="I7" s="32"/>
-      <c r="J7" s="34"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="F8" s="42" t="s">
+      <c r="I7" s="21"/>
+      <c r="J7" s="23"/>
+    </row>
+    <row r="8" spans="1:11" ht="16.8">
+      <c r="E8" s="49"/>
+      <c r="F8" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="70">
         <v>0</v>
       </c>
-      <c r="H8" s="34"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="34"/>
-    </row>
-    <row r="9" spans="1:11" s="45" customFormat="1" ht="41.4">
+      <c r="H8" s="23"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="23"/>
+    </row>
+    <row r="9" spans="1:11" s="45" customFormat="1" ht="50.4">
       <c r="A9" s="43" t="s">
         <v>11</v>
       </c>
@@ -3340,10 +3532,10 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="69.599999999999994" customHeight="1">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="46" t="s">
         <v>33</v>
       </c>
       <c r="C10" s="47" t="s">
@@ -3361,21 +3553,21 @@
       <c r="G10" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="48" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="62.4" customHeight="1">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="46" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="46" t="s">
         <v>63</v>
       </c>
       <c r="E11" s="47" t="s">
@@ -3387,12 +3579,12 @@
       <c r="G11" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="48" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="48.6" customHeight="1">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="46" t="s">
         <v>46</v>
       </c>
       <c r="B12" s="47" t="s">
@@ -3401,7 +3593,7 @@
       <c r="C12" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="46" t="s">
         <v>69</v>
       </c>
       <c r="E12" s="47" t="s">
@@ -3413,90 +3605,90 @@
       <c r="G12" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="48" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="49.2" customHeight="1">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="46" t="s">
         <v>69</v>
       </c>
       <c r="E13" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="41.4">
-      <c r="A14" s="16" t="s">
+      <c r="H13" s="48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="67.2">
+      <c r="A14" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="46" t="s">
         <v>51</v>
       </c>
       <c r="C14" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="46" t="s">
         <v>69</v>
       </c>
       <c r="E14" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="41.4">
-      <c r="A15" s="16" t="s">
+      <c r="H14" s="48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="50.4">
+      <c r="A15" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="46" t="s">
         <v>53</v>
       </c>
       <c r="C15" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="46" t="s">
         <v>69</v>
       </c>
       <c r="E15" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="H15" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="69">
-      <c r="A16" s="16" t="s">
+      <c r="H15" s="48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="84">
+      <c r="A16" s="46" t="s">
         <v>54</v>
       </c>
       <c r="B16" s="47" t="s">
@@ -3505,7 +3697,7 @@
       <c r="C16" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="46" t="s">
         <v>69</v>
       </c>
       <c r="E16" s="47" t="s">
@@ -3517,21 +3709,21 @@
       <c r="G16" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="H16" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="41.4">
-      <c r="A17" s="16" t="s">
+      <c r="H16" s="48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="67.2">
+      <c r="A17" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="46" t="s">
         <v>57</v>
       </c>
       <c r="C17" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="46" t="s">
         <v>69</v>
       </c>
       <c r="E17" s="47" t="s">
@@ -3543,12 +3735,12 @@
       <c r="G17" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="H17" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="41.4">
-      <c r="A18" s="16" t="s">
+      <c r="H17" s="48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="67.2">
+      <c r="A18" s="46" t="s">
         <v>58</v>
       </c>
       <c r="B18" s="47" t="s">
@@ -3557,7 +3749,7 @@
       <c r="C18" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="46" t="s">
         <v>69</v>
       </c>
       <c r="E18" s="47" t="s">
@@ -3569,12 +3761,12 @@
       <c r="G18" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="41.4">
-      <c r="A19" s="16" t="s">
+      <c r="H18" s="48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="67.2">
+      <c r="A19" s="46" t="s">
         <v>59</v>
       </c>
       <c r="B19" s="47" t="s">
@@ -3583,7 +3775,7 @@
       <c r="C19" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="46" t="s">
         <v>69</v>
       </c>
       <c r="E19" s="47" t="s">
@@ -3595,12 +3787,12 @@
       <c r="G19" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="48" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="67.8" customHeight="1">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="46" t="s">
         <v>60</v>
       </c>
       <c r="B20" s="47" t="s">
@@ -3609,7 +3801,7 @@
       <c r="C20" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="46" t="s">
         <v>69</v>
       </c>
       <c r="E20" s="47" t="s">
@@ -3621,180 +3813,181 @@
       <c r="G20" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="H20" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="27"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
+      <c r="H20" s="48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="17.399999999999999">
+      <c r="A21" s="49"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="48"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="27"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="27"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="46"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="46"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="27"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="27"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
     </row>
     <row r="28" spans="1:8" ht="14.4" customHeight="1">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="27"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="27"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="27"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="27"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="27"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="27"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="27"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="27"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
     </row>
     <row r="40" spans="1:7" ht="14.4" customHeight="1"/>
   </sheetData>
@@ -3805,9 +3998,9 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E5:F5"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H9 B22:B23" xr:uid="{D3DAC962-B0A1-4550-A348-76F18ADC62A1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B22:B23 H1:H1048576" xr:uid="{D3DAC962-B0A1-4550-A348-76F18ADC62A1}">
       <formula1>"Pass,Fail"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3817,7 +4010,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57977689-3AE3-4B2E-A947-3358541BF278}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultColWidth="18.33203125" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
@@ -3829,417 +4022,418 @@
     <col min="8" max="8" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="D1" s="78" t="s">
+    <row r="1" spans="1:10" ht="16.8">
+      <c r="D1" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="13" t="s">
+      <c r="E1" s="91"/>
+      <c r="F1" s="59" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="7"/>
     </row>
-    <row r="2" spans="1:10">
-      <c r="D2" s="78" t="s">
+    <row r="2" spans="1:10" ht="16.8">
+      <c r="D2" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="13" t="s">
+      <c r="E2" s="91"/>
+      <c r="F2" s="59" t="s">
         <v>22</v>
       </c>
       <c r="G2" s="7"/>
     </row>
-    <row r="3" spans="1:10">
-      <c r="D3" s="78" t="s">
+    <row r="3" spans="1:10" ht="16.8">
+      <c r="D3" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="78"/>
-      <c r="F3" s="15">
+      <c r="E3" s="91"/>
+      <c r="F3" s="60">
         <v>45516</v>
       </c>
-      <c r="G3" s="67"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="D4" s="78" t="s">
+      <c r="G3" s="36"/>
+    </row>
+    <row r="4" spans="1:10" ht="16.8">
+      <c r="D4" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="78"/>
-      <c r="F4" s="15">
+      <c r="E4" s="91"/>
+      <c r="F4" s="60">
         <v>41985</v>
       </c>
-      <c r="G4" s="67"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="D5" s="78" t="s">
+      <c r="G4" s="36"/>
+    </row>
+    <row r="5" spans="1:10" ht="16.8">
+      <c r="D5" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="13"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="59"/>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:10">
-      <c r="D6" s="7"/>
-      <c r="E6" s="7" t="s">
+    <row r="6" spans="1:10" ht="16.8">
+      <c r="D6" s="61"/>
+      <c r="E6" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="61">
         <v>12</v>
       </c>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:10">
-      <c r="D7" s="7"/>
-      <c r="E7" s="7" t="s">
+    <row r="7" spans="1:10" ht="16.8">
+      <c r="D7" s="61"/>
+      <c r="E7" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="61">
         <v>11</v>
       </c>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" ht="16.8">
       <c r="A8" s="6"/>
       <c r="B8" s="1"/>
       <c r="C8" s="3"/>
-      <c r="E8" s="9" t="s">
+      <c r="D8" s="46"/>
+      <c r="E8" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="63">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="20.399999999999999">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:10" s="46" customFormat="1" ht="50.4">
+      <c r="A9" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="44" t="s">
         <v>338</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="44" t="s">
         <v>339</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="44" t="s">
         <v>340</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="G9" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="H9" s="48" t="s">
+      <c r="H9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="48" t="s">
+      <c r="I9" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="48" t="s">
+      <c r="J9" s="43" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="58.2" customHeight="1">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="E10" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="G10" s="46" t="s">
+      <c r="G10" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="H10" s="46" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A11" s="46" t="s">
+      <c r="H10" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="48.6" customHeight="1">
+      <c r="A11" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="46" t="s">
+      <c r="E11" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="46" t="s">
+      <c r="F11" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="G11" s="46" t="s">
+      <c r="G11" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="H11" s="46" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A12" s="46" t="s">
+      <c r="H11" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="49.2" customHeight="1">
+      <c r="A12" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E12" s="46" t="s">
+      <c r="E12" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="G12" s="46" t="s">
+      <c r="G12" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="46" t="s">
+      <c r="H12" s="50" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="46" t="s">
+      <c r="E13" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="F13" s="46" t="s">
+      <c r="F13" s="50" t="s">
         <v>148</v>
       </c>
-      <c r="G13" s="46" t="s">
+      <c r="G13" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="H13" s="46" t="s">
+      <c r="H13" s="50" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="F14" s="46" t="s">
+      <c r="F14" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="H14" s="46" t="s">
+      <c r="H14" s="50" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="42" customHeight="1">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="46" t="s">
+      <c r="C15" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="46" t="s">
+      <c r="E15" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="F15" s="46" t="s">
+      <c r="F15" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="G15" s="46" t="s">
+      <c r="G15" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="H15" s="46" t="s">
+      <c r="H15" s="50" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D16" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E16" s="46" t="s">
+      <c r="E16" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="F16" s="46" t="s">
+      <c r="F16" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="G16" s="46" t="s">
+      <c r="G16" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="H16" s="46" t="s">
+      <c r="H16" s="50" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="28.8" customHeight="1">
-      <c r="A17" s="46" t="s">
+      <c r="A17" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E17" s="46" t="s">
+      <c r="E17" s="50" t="s">
         <v>141</v>
       </c>
-      <c r="F17" s="46" t="s">
+      <c r="F17" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="G17" s="46" t="s">
+      <c r="G17" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="H17" s="46" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="55.2">
-      <c r="A18" s="46" t="s">
+      <c r="H17" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="67.2">
+      <c r="A18" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="46" t="s">
+      <c r="D18" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E18" s="46" t="s">
+      <c r="E18" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="F18" s="46" t="s">
+      <c r="F18" s="50" t="s">
         <v>152</v>
       </c>
-      <c r="G18" s="46" t="s">
+      <c r="G18" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="H18" s="46" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="27.6">
-      <c r="A19" s="46" t="s">
+      <c r="H18" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="33.6">
+      <c r="A19" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="D19" s="46" t="s">
+      <c r="D19" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E19" s="46" t="s">
+      <c r="E19" s="50" t="s">
         <v>145</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="F19" s="49" t="s">
         <v>146</v>
       </c>
-      <c r="G19" s="46" t="s">
+      <c r="G19" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="H19" s="46" t="s">
+      <c r="H19" s="50" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8" customHeight="1">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="D20" s="46" t="s">
+      <c r="D20" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="46" t="s">
+      <c r="E20" s="50" t="s">
         <v>328</v>
       </c>
-      <c r="F20" s="46" t="s">
+      <c r="F20" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="G20" s="46" t="s">
+      <c r="G20" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="H20" s="46" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="28.2">
-      <c r="A21" s="46" t="s">
+      <c r="H20" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="67.2">
+      <c r="A21" s="50" t="s">
         <v>322</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="46" t="s">
         <v>323</v>
       </c>
       <c r="C21" s="47" t="s">
         <v>327</v>
       </c>
-      <c r="D21" s="46" t="s">
+      <c r="D21" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E21" s="46" t="s">
+      <c r="E21" s="50" t="s">
         <v>324</v>
       </c>
       <c r="F21" s="47" t="s">
@@ -4248,9 +4442,49 @@
       <c r="G21" s="47" t="s">
         <v>326</v>
       </c>
-      <c r="H21" s="46" t="s">
-        <v>21</v>
-      </c>
+      <c r="H21" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="17.399999999999999">
+      <c r="A22" s="51"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+    </row>
+    <row r="23" spans="1:8" ht="17.399999999999999">
+      <c r="A23" s="51"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+    </row>
+    <row r="24" spans="1:8" ht="17.399999999999999">
+      <c r="A24" s="51"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+    </row>
+    <row r="25" spans="1:8" ht="17.399999999999999">
+      <c r="A25" s="51"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4260,9 +4494,9 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D5:E5"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H9" xr:uid="{53FB3CC1-77D4-4E2D-BC39-D97339493EF7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576" xr:uid="{53FB3CC1-77D4-4E2D-BC39-D97339493EF7}">
       <formula1>"Pass,Fail"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4275,608 +4509,1138 @@
   <dimension ref="A1:I31"/>
   <sheetFormatPr defaultColWidth="34.33203125" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="34.33203125" style="10"/>
-    <col min="4" max="4" width="63.44140625" style="10" customWidth="1"/>
-    <col min="5" max="6" width="34.33203125" style="10"/>
-    <col min="7" max="7" width="8.33203125" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="34.33203125" style="10"/>
+    <col min="1" max="1" width="11.21875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" style="9" customWidth="1"/>
+    <col min="3" max="3" width="34.33203125" style="9"/>
+    <col min="4" max="4" width="63.44140625" style="9" customWidth="1"/>
+    <col min="5" max="6" width="34.33203125" style="9"/>
+    <col min="7" max="7" width="8.33203125" style="9" customWidth="1"/>
+    <col min="8" max="16384" width="34.33203125" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="D1" s="28" t="s">
+      <c r="A1" s="18"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="41"/>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="D2" s="28" t="s">
+      <c r="F1" s="64"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.8">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="41"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="D3" s="28" t="s">
+      <c r="F2" s="64"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" spans="1:9" ht="16.8">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="52">
+      <c r="E3" s="75">
         <v>45516</v>
       </c>
-      <c r="F3" s="53"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="D4" s="28" t="s">
+      <c r="F3" s="73"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+    </row>
+    <row r="4" spans="1:9" ht="16.8">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="52">
+      <c r="E4" s="75">
         <v>41985</v>
       </c>
-      <c r="F4" s="53"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="D5" s="28" t="s">
+      <c r="F4" s="73"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" spans="1:9" ht="16.8">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="51"/>
-      <c r="F5" s="41"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="D6" s="41" t="s">
+      <c r="E5" s="74"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+    </row>
+    <row r="6" spans="1:9" ht="16.8">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="41">
-        <v>21</v>
-      </c>
-      <c r="F6" s="41"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="D7" s="41" t="s">
+      <c r="E6" s="68">
+        <v>21</v>
+      </c>
+      <c r="F6" s="64"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+    </row>
+    <row r="7" spans="1:9" ht="16.8">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="68">
         <v>20</v>
       </c>
-      <c r="F7" s="41"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="D8" s="41" t="s">
+      <c r="F7" s="64"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" spans="1:9" ht="16.8">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="76">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" s="57" customFormat="1" ht="28.2" thickBot="1">
-      <c r="A9" s="54" t="s">
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+    </row>
+    <row r="9" spans="1:9" s="56" customFormat="1" ht="51" thickBot="1">
+      <c r="A9" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="54" t="s">
+      <c r="F9" s="52" t="s">
         <v>185</v>
       </c>
-      <c r="G9" s="55" t="s">
+      <c r="G9" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="55" t="s">
+      <c r="H9" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="56" t="s">
+      <c r="I9" s="55" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="121.8" customHeight="1" thickBot="1">
-      <c r="A10" s="58" t="s">
+    <row r="10" spans="1:9" s="49" customFormat="1" ht="121.8" customHeight="1" thickBot="1">
+      <c r="A10" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="57" t="s">
         <v>187</v>
       </c>
-      <c r="D10" s="58" t="s">
+      <c r="D10" s="57" t="s">
         <v>188</v>
       </c>
-      <c r="E10" s="58" t="s">
+      <c r="E10" s="57" t="s">
         <v>189</v>
       </c>
-      <c r="F10" s="58" t="s">
+      <c r="F10" s="57" t="s">
         <v>189</v>
       </c>
-      <c r="G10" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="144" customHeight="1" thickBot="1">
-      <c r="A11" s="58" t="s">
+      <c r="G10" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="49" customFormat="1" ht="144" customHeight="1" thickBot="1">
+      <c r="A11" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="B11" s="58" t="s">
+      <c r="B11" s="57" t="s">
         <v>184</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="57" t="s">
         <v>190</v>
       </c>
-      <c r="D11" s="58" t="s">
+      <c r="D11" s="57" t="s">
         <v>191</v>
       </c>
-      <c r="E11" s="58" t="s">
+      <c r="E11" s="57" t="s">
         <v>192</v>
       </c>
-      <c r="F11" s="58" t="s">
+      <c r="F11" s="57" t="s">
         <v>192</v>
       </c>
-      <c r="G11" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="134.4" customHeight="1" thickBot="1">
-      <c r="A12" s="58" t="s">
+      <c r="G11" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="49" customFormat="1" ht="134.4" customHeight="1" thickBot="1">
+      <c r="A12" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="57" t="s">
         <v>161</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="57" t="s">
         <v>193</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="D12" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="E12" s="58" t="s">
+      <c r="E12" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="F12" s="58" t="s">
+      <c r="F12" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="G12" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="126.6" customHeight="1" thickBot="1">
-      <c r="A13" s="58" t="s">
+      <c r="G12" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="49" customFormat="1" ht="126.6" customHeight="1" thickBot="1">
+      <c r="A13" s="57" t="s">
         <v>162</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="57" t="s">
         <v>196</v>
       </c>
-      <c r="D13" s="58" t="s">
+      <c r="D13" s="57" t="s">
         <v>197</v>
       </c>
-      <c r="E13" s="58" t="s">
+      <c r="E13" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="F13" s="58" t="s">
+      <c r="F13" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="G13" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="120" customHeight="1" thickBot="1">
-      <c r="A14" s="58" t="s">
+      <c r="G13" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="49" customFormat="1" ht="120" customHeight="1" thickBot="1">
+      <c r="A14" s="57" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="57" t="s">
         <v>200</v>
       </c>
-      <c r="D14" s="58" t="s">
+      <c r="D14" s="57" t="s">
         <v>201</v>
       </c>
-      <c r="E14" s="58" t="s">
+      <c r="E14" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="F14" s="58" t="s">
+      <c r="F14" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="G14" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="136.80000000000001" customHeight="1" thickBot="1">
-      <c r="A15" s="58" t="s">
+      <c r="G14" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="49" customFormat="1" ht="136.80000000000001" customHeight="1" thickBot="1">
+      <c r="A15" s="57" t="s">
         <v>164</v>
       </c>
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="57" t="s">
         <v>203</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="57" t="s">
         <v>204</v>
       </c>
-      <c r="D15" s="58" t="s">
+      <c r="D15" s="57" t="s">
         <v>205</v>
       </c>
-      <c r="E15" s="58" t="s">
+      <c r="E15" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="F15" s="58" t="s">
+      <c r="F15" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="G15" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="156.6" customHeight="1" thickBot="1">
-      <c r="A16" s="58" t="s">
+      <c r="G15" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="49" customFormat="1" ht="156.6" customHeight="1" thickBot="1">
+      <c r="A16" s="57" t="s">
         <v>165</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="57" t="s">
         <v>156</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="57" t="s">
         <v>207</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="57" t="s">
         <v>208</v>
       </c>
-      <c r="E16" s="58" t="s">
+      <c r="E16" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="F16" s="58" t="s">
+      <c r="F16" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="G16" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="150" customHeight="1" thickBot="1">
-      <c r="A17" s="58" t="s">
+      <c r="G16" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="49" customFormat="1" ht="150" customHeight="1" thickBot="1">
+      <c r="A17" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="57" t="s">
         <v>210</v>
       </c>
-      <c r="D17" s="58" t="s">
+      <c r="D17" s="57" t="s">
         <v>211</v>
       </c>
-      <c r="E17" s="58" t="s">
+      <c r="E17" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="F17" s="58" t="s">
+      <c r="F17" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="G17" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="126" customHeight="1" thickBot="1">
-      <c r="A18" s="58" t="s">
+      <c r="G17" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="49" customFormat="1" ht="126" customHeight="1" thickBot="1">
+      <c r="A18" s="57" t="s">
         <v>168</v>
       </c>
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="57" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="D18" s="58" t="s">
+      <c r="D18" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="E18" s="57" t="s">
         <v>215</v>
       </c>
-      <c r="F18" s="58" t="s">
+      <c r="F18" s="57" t="s">
         <v>215</v>
       </c>
-      <c r="G18" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="60.6" customHeight="1" thickBot="1">
-      <c r="A19" s="58" t="s">
+      <c r="G18" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="49" customFormat="1" ht="60.6" customHeight="1" thickBot="1">
+      <c r="A19" s="57" t="s">
         <v>170</v>
       </c>
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="57" t="s">
         <v>216</v>
       </c>
-      <c r="D19" s="58" t="s">
+      <c r="D19" s="57" t="s">
         <v>217</v>
       </c>
-      <c r="E19" s="58" t="s">
+      <c r="E19" s="57" t="s">
         <v>218</v>
       </c>
-      <c r="F19" s="58" t="s">
+      <c r="F19" s="57" t="s">
         <v>218</v>
       </c>
-      <c r="G19" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="86.4" customHeight="1" thickBot="1">
-      <c r="A20" s="58" t="s">
+      <c r="G19" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="49" customFormat="1" ht="86.4" customHeight="1" thickBot="1">
+      <c r="A20" s="57" t="s">
         <v>172</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="57" t="s">
         <v>219</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="57" t="s">
         <v>220</v>
       </c>
-      <c r="D20" s="58" t="s">
+      <c r="D20" s="57" t="s">
         <v>221</v>
       </c>
-      <c r="E20" s="58" t="s">
+      <c r="E20" s="57" t="s">
         <v>344</v>
       </c>
-      <c r="F20" s="58" t="s">
+      <c r="F20" s="57" t="s">
         <v>344</v>
       </c>
-      <c r="G20" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="99" customHeight="1" thickBot="1">
-      <c r="A21" s="58" t="s">
+      <c r="G20" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="49" customFormat="1" ht="99" customHeight="1" thickBot="1">
+      <c r="A21" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="57" t="s">
         <v>223</v>
       </c>
-      <c r="D21" s="58" t="s">
+      <c r="D21" s="57" t="s">
         <v>224</v>
       </c>
-      <c r="E21" s="58" t="s">
+      <c r="E21" s="57" t="s">
         <v>345</v>
       </c>
-      <c r="F21" s="58" t="s">
+      <c r="F21" s="57" t="s">
         <v>225</v>
       </c>
-      <c r="G21" s="59" t="s">
+      <c r="G21" s="58" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="71.400000000000006" customHeight="1" thickBot="1">
-      <c r="A22" s="58" t="s">
+    <row r="22" spans="1:7" s="49" customFormat="1" ht="71.400000000000006" customHeight="1" thickBot="1">
+      <c r="A22" s="57" t="s">
         <v>174</v>
       </c>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="57" t="s">
         <v>226</v>
       </c>
-      <c r="D22" s="58" t="s">
+      <c r="D22" s="57" t="s">
         <v>227</v>
       </c>
-      <c r="E22" s="58" t="s">
+      <c r="E22" s="57" t="s">
         <v>228</v>
       </c>
-      <c r="F22" s="58" t="s">
+      <c r="F22" s="57" t="s">
         <v>228</v>
       </c>
-      <c r="G22" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="93.6" customHeight="1" thickBot="1">
-      <c r="A23" s="58" t="s">
+      <c r="G22" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="49" customFormat="1" ht="93.6" customHeight="1" thickBot="1">
+      <c r="A23" s="57" t="s">
         <v>176</v>
       </c>
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="57" t="s">
         <v>229</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="57" t="s">
         <v>230</v>
       </c>
-      <c r="D23" s="58" t="s">
+      <c r="D23" s="57" t="s">
         <v>231</v>
       </c>
-      <c r="E23" s="58" t="s">
+      <c r="E23" s="57" t="s">
         <v>232</v>
       </c>
-      <c r="F23" s="58" t="s">
+      <c r="F23" s="57" t="s">
         <v>232</v>
       </c>
-      <c r="G23" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="57.6" customHeight="1" thickBot="1">
-      <c r="A24" s="58" t="s">
+      <c r="G23" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="49" customFormat="1" ht="57.6" customHeight="1" thickBot="1">
+      <c r="A24" s="57" t="s">
         <v>177</v>
       </c>
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="57" t="s">
         <v>178</v>
       </c>
-      <c r="C24" s="58" t="s">
+      <c r="C24" s="57" t="s">
         <v>233</v>
       </c>
-      <c r="D24" s="58" t="s">
+      <c r="D24" s="57" t="s">
         <v>234</v>
       </c>
-      <c r="E24" s="58" t="s">
+      <c r="E24" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="F24" s="58" t="s">
+      <c r="F24" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="G24" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="72" customHeight="1" thickBot="1">
-      <c r="A25" s="58" t="s">
+      <c r="G24" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="49" customFormat="1" ht="72" customHeight="1" thickBot="1">
+      <c r="A25" s="57" t="s">
         <v>179</v>
       </c>
-      <c r="B25" s="58" t="s">
+      <c r="B25" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="57" t="s">
         <v>235</v>
       </c>
-      <c r="D25" s="58" t="s">
+      <c r="D25" s="57" t="s">
         <v>236</v>
       </c>
-      <c r="E25" s="58" t="s">
+      <c r="E25" s="57" t="s">
         <v>237</v>
       </c>
-      <c r="F25" s="58" t="s">
+      <c r="F25" s="57" t="s">
         <v>237</v>
       </c>
-      <c r="G25" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="57.6" customHeight="1" thickBot="1">
-      <c r="A26" s="58" t="s">
+      <c r="G25" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="49" customFormat="1" ht="57.6" customHeight="1" thickBot="1">
+      <c r="A26" s="57" t="s">
         <v>180</v>
       </c>
-      <c r="B26" s="58" t="s">
+      <c r="B26" s="57" t="s">
         <v>238</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="D26" s="58" t="s">
+      <c r="D26" s="57" t="s">
         <v>240</v>
       </c>
-      <c r="E26" s="58" t="s">
+      <c r="E26" s="57" t="s">
         <v>225</v>
       </c>
-      <c r="F26" s="58" t="s">
+      <c r="F26" s="57" t="s">
         <v>225</v>
       </c>
-      <c r="G26" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="78" customHeight="1" thickBot="1">
-      <c r="A27" s="58" t="s">
+      <c r="G26" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="49" customFormat="1" ht="78" customHeight="1" thickBot="1">
+      <c r="A27" s="57" t="s">
         <v>181</v>
       </c>
-      <c r="B27" s="58" t="s">
+      <c r="B27" s="57" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="57" t="s">
         <v>242</v>
       </c>
-      <c r="D27" s="58" t="s">
+      <c r="D27" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="E27" s="58" t="s">
+      <c r="E27" s="57" t="s">
         <v>243</v>
       </c>
-      <c r="F27" s="58" t="s">
+      <c r="F27" s="57" t="s">
         <v>243</v>
       </c>
-      <c r="G27" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="57.6" customHeight="1" thickBot="1">
-      <c r="A28" s="58" t="s">
+      <c r="G27" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="49" customFormat="1" ht="154.19999999999999" customHeight="1" thickBot="1">
+      <c r="A28" s="57" t="s">
         <v>182</v>
       </c>
-      <c r="B28" s="58" t="s">
+      <c r="B28" s="57" t="s">
         <v>244</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="C28" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="D28" s="58" t="s">
+      <c r="D28" s="57" t="s">
         <v>246</v>
       </c>
-      <c r="E28" s="58" t="s">
+      <c r="E28" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="F28" s="58" t="s">
+      <c r="F28" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="G28" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="119.4" thickBot="1">
-      <c r="A29" s="58" t="s">
+      <c r="G28" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="49" customFormat="1" ht="151.80000000000001" thickBot="1">
+      <c r="A29" s="57" t="s">
         <v>183</v>
       </c>
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="57" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="58" t="s">
+      <c r="C29" s="57" t="s">
         <v>248</v>
       </c>
-      <c r="D29" s="58" t="s">
+      <c r="D29" s="57" t="s">
         <v>249</v>
       </c>
-      <c r="E29" s="58" t="s">
+      <c r="E29" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="F29" s="58" t="s">
+      <c r="F29" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="G29" s="59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="119.4" thickBot="1">
-      <c r="A30" s="58" t="s">
+      <c r="G29" s="58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="49" customFormat="1" ht="151.80000000000001" thickBot="1">
+      <c r="A30" s="57" t="s">
         <v>250</v>
       </c>
-      <c r="B30" s="58" t="s">
+      <c r="B30" s="57" t="s">
         <v>251</v>
       </c>
-      <c r="C30" s="58" t="s">
+      <c r="C30" s="57" t="s">
         <v>252</v>
       </c>
-      <c r="D30" s="58" t="s">
+      <c r="D30" s="57" t="s">
         <v>253</v>
       </c>
-      <c r="E30" s="58" t="s">
+      <c r="E30" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="F30" s="58" t="s">
+      <c r="F30" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="G30" s="59" t="s">
+      <c r="G30" s="58" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="49"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
+      <c r="A31" s="31"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G9" xr:uid="{48F02694-4A7F-4004-BB0C-4BD712CDCF97}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{48F02694-4A7F-4004-BB0C-4BD712CDCF97}">
+      <formula1>"Pass,Fail"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD2EB7C3-895C-4393-96EC-492D6FAB3804}">
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr defaultColWidth="28" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="20.77734375" customWidth="1"/>
+    <col min="5" max="5" width="64.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="16.8">
+      <c r="A1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="77"/>
+      <c r="E1" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="29"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+    </row>
+    <row r="2" spans="1:10" ht="16.8">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="65" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="77"/>
+      <c r="E2" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="29"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+    </row>
+    <row r="3" spans="1:10" ht="16.8">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="77"/>
+      <c r="E3" s="75">
+        <v>45516</v>
+      </c>
+      <c r="F3" s="32"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+    </row>
+    <row r="4" spans="1:10" ht="16.8">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="77"/>
+      <c r="E4" s="75">
+        <v>41985</v>
+      </c>
+      <c r="F4" s="32"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:10" ht="16.8">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="77"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" spans="1:10" ht="16.8">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68">
+        <v>21</v>
+      </c>
+      <c r="F6" s="29"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" spans="1:10" ht="16.8">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68">
+        <v>20</v>
+      </c>
+      <c r="F7" s="29"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" spans="1:10" ht="16.8">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="68"/>
+      <c r="E8" s="76">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+    </row>
+    <row r="9" spans="1:10" s="37" customFormat="1" ht="33.6">
+      <c r="A9" s="78" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="79" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="79" t="s">
+        <v>339</v>
+      </c>
+      <c r="E9" s="78" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="78" t="s">
+        <v>185</v>
+      </c>
+      <c r="H9" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="81" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="84" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="184.8">
+      <c r="A10" s="82" t="s">
+        <v>354</v>
+      </c>
+      <c r="B10" s="82" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="82" t="s">
+        <v>355</v>
+      </c>
+      <c r="D10" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="E10" s="83" t="s">
+        <v>387</v>
+      </c>
+      <c r="F10" s="82" t="s">
+        <v>347</v>
+      </c>
+      <c r="G10" s="82" t="s">
+        <v>347</v>
+      </c>
+      <c r="H10" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+    </row>
+    <row r="11" spans="1:10" ht="168">
+      <c r="A11" s="82" t="s">
+        <v>356</v>
+      </c>
+      <c r="B11" s="82" t="s">
+        <v>357</v>
+      </c>
+      <c r="C11" s="82" t="s">
+        <v>358</v>
+      </c>
+      <c r="D11" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="E11" s="83" t="s">
+        <v>388</v>
+      </c>
+      <c r="F11" s="82" t="s">
+        <v>346</v>
+      </c>
+      <c r="G11" s="82" t="s">
+        <v>346</v>
+      </c>
+      <c r="H11" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+    </row>
+    <row r="12" spans="1:10" ht="168">
+      <c r="A12" s="82" t="s">
+        <v>359</v>
+      </c>
+      <c r="B12" s="82" t="s">
+        <v>360</v>
+      </c>
+      <c r="C12" s="82" t="s">
+        <v>361</v>
+      </c>
+      <c r="D12" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="E12" s="83" t="s">
+        <v>389</v>
+      </c>
+      <c r="F12" s="82" t="s">
+        <v>392</v>
+      </c>
+      <c r="G12" s="82" t="s">
+        <v>392</v>
+      </c>
+      <c r="H12" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+    </row>
+    <row r="13" spans="1:10" ht="168">
+      <c r="A13" s="82" t="s">
+        <v>362</v>
+      </c>
+      <c r="B13" s="82" t="s">
+        <v>363</v>
+      </c>
+      <c r="C13" s="82" t="s">
+        <v>364</v>
+      </c>
+      <c r="D13" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="E13" s="83" t="s">
+        <v>390</v>
+      </c>
+      <c r="F13" s="82" t="s">
+        <v>393</v>
+      </c>
+      <c r="G13" s="82" t="s">
+        <v>393</v>
+      </c>
+      <c r="H13" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+    </row>
+    <row r="14" spans="1:10" ht="168">
+      <c r="A14" s="82" t="s">
+        <v>365</v>
+      </c>
+      <c r="B14" s="82" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" s="82" t="s">
+        <v>366</v>
+      </c>
+      <c r="D14" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="E14" s="82" t="s">
+        <v>402</v>
+      </c>
+      <c r="F14" s="82" t="s">
+        <v>394</v>
+      </c>
+      <c r="G14" s="82" t="s">
+        <v>394</v>
+      </c>
+      <c r="H14" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+    </row>
+    <row r="15" spans="1:10" ht="168">
+      <c r="A15" s="82" t="s">
+        <v>367</v>
+      </c>
+      <c r="B15" s="82" t="s">
+        <v>368</v>
+      </c>
+      <c r="C15" s="82" t="s">
+        <v>369</v>
+      </c>
+      <c r="D15" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="E15" s="83" t="s">
+        <v>391</v>
+      </c>
+      <c r="F15" s="82" t="s">
+        <v>348</v>
+      </c>
+      <c r="G15" s="82" t="s">
+        <v>348</v>
+      </c>
+      <c r="H15" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+    </row>
+    <row r="16" spans="1:10" ht="168">
+      <c r="A16" s="82" t="s">
+        <v>370</v>
+      </c>
+      <c r="B16" s="82" t="s">
+        <v>371</v>
+      </c>
+      <c r="C16" s="82" t="s">
+        <v>372</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="E16" s="83" t="s">
+        <v>395</v>
+      </c>
+      <c r="F16" s="82" t="s">
+        <v>373</v>
+      </c>
+      <c r="G16" s="82" t="s">
+        <v>373</v>
+      </c>
+      <c r="H16" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+    </row>
+    <row r="17" spans="1:10" ht="151.19999999999999">
+      <c r="A17" s="82" t="s">
+        <v>374</v>
+      </c>
+      <c r="B17" s="82" t="s">
+        <v>375</v>
+      </c>
+      <c r="C17" s="82" t="s">
+        <v>376</v>
+      </c>
+      <c r="D17" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="E17" s="82" t="s">
+        <v>397</v>
+      </c>
+      <c r="F17" s="82" t="s">
+        <v>396</v>
+      </c>
+      <c r="G17" s="82" t="s">
+        <v>396</v>
+      </c>
+      <c r="H17" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+    </row>
+    <row r="18" spans="1:10" ht="151.19999999999999">
+      <c r="A18" s="82" t="s">
+        <v>378</v>
+      </c>
+      <c r="B18" s="82" t="s">
+        <v>379</v>
+      </c>
+      <c r="C18" s="82" t="s">
+        <v>380</v>
+      </c>
+      <c r="D18" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="E18" s="82" t="s">
+        <v>398</v>
+      </c>
+      <c r="F18" s="82" t="s">
+        <v>377</v>
+      </c>
+      <c r="G18" s="82" t="s">
+        <v>377</v>
+      </c>
+      <c r="H18" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+    </row>
+    <row r="19" spans="1:10" ht="184.8">
+      <c r="A19" s="82" t="s">
+        <v>381</v>
+      </c>
+      <c r="B19" s="82" t="s">
+        <v>382</v>
+      </c>
+      <c r="C19" s="82" t="s">
+        <v>383</v>
+      </c>
+      <c r="D19" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="E19" s="82" t="s">
+        <v>399</v>
+      </c>
+      <c r="F19" s="82" t="s">
+        <v>348</v>
+      </c>
+      <c r="G19" s="82" t="s">
+        <v>404</v>
+      </c>
+      <c r="H19" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+    </row>
+    <row r="20" spans="1:10" ht="151.19999999999999">
+      <c r="A20" s="82" t="s">
+        <v>384</v>
+      </c>
+      <c r="B20" s="82" t="s">
+        <v>385</v>
+      </c>
+      <c r="C20" s="82" t="s">
+        <v>386</v>
+      </c>
+      <c r="D20" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="E20" s="82" t="s">
+        <v>400</v>
+      </c>
+      <c r="F20" s="82" t="s">
+        <v>348</v>
+      </c>
+      <c r="G20" s="82" t="s">
+        <v>348</v>
+      </c>
+      <c r="H20" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G8 H1:H1048576" xr:uid="{A6DA4C4D-BB53-4600-88F2-12BFC0CFFED4}">
       <formula1>"Pass,Fail"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4884,342 +5648,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407BF401-235A-4B80-82D4-2E02A2B9E0B2}">
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="30.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="9" max="9" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C1" t="s">
-        <v>348</v>
-      </c>
-      <c r="D1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E1" t="s">
-        <v>350</v>
-      </c>
-      <c r="F1" t="s">
-        <v>351</v>
-      </c>
-      <c r="G1" t="s">
-        <v>352</v>
-      </c>
-      <c r="H1" t="s">
-        <v>353</v>
-      </c>
-      <c r="I1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>355</v>
-      </c>
-      <c r="B2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D2" t="s">
-        <v>364</v>
-      </c>
-      <c r="E2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F2" s="68" t="s">
-        <v>359</v>
-      </c>
-      <c r="G2" s="69" t="s">
-        <v>360</v>
-      </c>
-      <c r="H2" t="s">
-        <v>361</v>
-      </c>
-      <c r="I2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C3" t="s">
-        <v>357</v>
-      </c>
-      <c r="E3" t="s">
-        <v>358</v>
-      </c>
-      <c r="F3" s="68" t="s">
-        <v>365</v>
-      </c>
-      <c r="G3" t="s">
-        <v>360</v>
-      </c>
-      <c r="H3" t="s">
-        <v>361</v>
-      </c>
-      <c r="I3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>355</v>
-      </c>
-      <c r="B4" t="s">
-        <v>356</v>
-      </c>
-      <c r="C4" t="s">
-        <v>357</v>
-      </c>
-      <c r="D4" t="s">
-        <v>364</v>
-      </c>
-      <c r="F4" s="68" t="s">
-        <v>366</v>
-      </c>
-      <c r="G4" t="s">
-        <v>360</v>
-      </c>
-      <c r="H4" t="s">
-        <v>361</v>
-      </c>
-      <c r="I4" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>355</v>
-      </c>
-      <c r="B5" t="s">
-        <v>356</v>
-      </c>
-      <c r="C5" t="s">
-        <v>357</v>
-      </c>
-      <c r="D5" t="s">
-        <v>364</v>
-      </c>
-      <c r="E5" t="s">
-        <v>358</v>
-      </c>
-      <c r="F5" s="68"/>
-      <c r="G5" t="s">
-        <v>360</v>
-      </c>
-      <c r="H5" t="s">
-        <v>361</v>
-      </c>
-      <c r="I5" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>355</v>
-      </c>
-      <c r="B6" t="s">
-        <v>356</v>
-      </c>
-      <c r="C6" t="s">
-        <v>357</v>
-      </c>
-      <c r="D6" t="s">
-        <v>364</v>
-      </c>
-      <c r="E6" t="s">
-        <v>358</v>
-      </c>
-      <c r="F6" s="68" t="s">
-        <v>367</v>
-      </c>
-      <c r="H6" t="s">
-        <v>361</v>
-      </c>
-      <c r="I6" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>355</v>
-      </c>
-      <c r="B7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C7" t="s">
-        <v>357</v>
-      </c>
-      <c r="D7" t="s">
-        <v>364</v>
-      </c>
-      <c r="E7" t="s">
-        <v>358</v>
-      </c>
-      <c r="F7" s="68" t="s">
-        <v>368</v>
-      </c>
-      <c r="G7" t="s">
-        <v>360</v>
-      </c>
-      <c r="I7" s="70" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="10" customFormat="1" ht="34.200000000000003" customHeight="1">
-      <c r="A8" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="F8" s="71" t="s">
-        <v>369</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>355</v>
-      </c>
-      <c r="B9" t="s">
-        <v>356</v>
-      </c>
-      <c r="C9" t="s">
-        <v>357</v>
-      </c>
-      <c r="D9" t="s">
-        <v>364</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="F9" s="71" t="s">
-        <v>369</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="I9" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>355</v>
-      </c>
-      <c r="B10" t="s">
-        <v>356</v>
-      </c>
-      <c r="C10" t="s">
-        <v>357</v>
-      </c>
-      <c r="D10" t="s">
-        <v>364</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="F10" s="71" t="s">
-        <v>377</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="I10" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>355</v>
-      </c>
-      <c r="B11" t="s">
-        <v>356</v>
-      </c>
-      <c r="C11" t="s">
-        <v>357</v>
-      </c>
-      <c r="D11" t="s">
-        <v>364</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="F11" s="71" t="s">
-        <v>377</v>
-      </c>
-      <c r="G11" t="s">
-        <v>379</v>
-      </c>
-      <c r="I11" s="70" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>355</v>
-      </c>
-      <c r="B12" t="s">
-        <v>356</v>
-      </c>
-      <c r="C12" t="s">
-        <v>357</v>
-      </c>
-      <c r="D12" t="s">
-        <v>364</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="F12">
-        <v>2122</v>
-      </c>
-      <c r="G12" t="s">
-        <v>380</v>
-      </c>
-      <c r="I12" s="70" t="s">
-        <v>373</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{B5D9ABFE-A300-4437-A125-B1E52D1C34F4}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E0F943-41AD-463A-9AD1-A9D21A7C73EE}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
@@ -5229,100 +5660,121 @@
     <col min="5" max="5" width="22.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A1" s="63" t="s">
+    <row r="1" spans="1:5" ht="24.6" customHeight="1">
+      <c r="A1" s="39" t="s">
         <v>329</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="39" t="s">
         <v>330</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="C1" s="39" t="s">
         <v>331</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="39" t="s">
         <v>332</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="39" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
+    <row r="2" spans="1:5" ht="16.8">
+      <c r="A2" s="40">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="40">
         <v>15</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="40">
         <v>13</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="40">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
+    <row r="3" spans="1:5" ht="16.8">
+      <c r="A3" s="40">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="40" t="s">
         <v>335</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="40">
         <v>11</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="40">
         <v>11</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
+    <row r="4" spans="1:5" ht="16.8">
+      <c r="A4" s="40">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="40" t="s">
         <v>336</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="40">
         <v>12</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="40">
         <v>12</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
+    <row r="5" spans="1:5" ht="16.8">
+      <c r="A5" s="40">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="40" t="s">
         <v>337</v>
       </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="40">
+        <v>21</v>
+      </c>
+      <c r="D5" s="40">
         <v>20</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="40">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="C6">
-        <v>58</v>
-      </c>
-      <c r="D6" s="66">
-        <v>56</v>
-      </c>
-      <c r="E6" s="65">
-        <v>2</v>
+    <row r="6" spans="1:5" ht="16.8">
+      <c r="A6" s="40">
+        <v>5</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>401</v>
+      </c>
+      <c r="C6" s="40">
+        <v>11</v>
+      </c>
+      <c r="D6" s="40">
+        <v>11</v>
+      </c>
+      <c r="E6" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16.8">
+      <c r="A7" s="40"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40">
+        <f>SUM(C2:C6)</f>
+        <v>70</v>
+      </c>
+      <c r="D7" s="41">
+        <f>SUM(D2:D6)</f>
+        <v>67</v>
+      </c>
+      <c r="E7" s="42">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
